--- a/output/yearly_total_coral_cover_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_39_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.28702847064048</v>
+        <v>1.259834059232843</v>
       </c>
       <c r="C3" t="n">
-        <v>4.631666629958566</v>
+        <v>4.665104956765211</v>
       </c>
       <c r="D3" t="n">
-        <v>6.043074456348063</v>
+        <v>6.131471019638446</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96176955694711</v>
+        <v>12.0564100356365</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.46024595962055</v>
+        <v>1.394275922410535</v>
       </c>
       <c r="C4" t="n">
-        <v>5.123597155928261</v>
+        <v>5.21280215945036</v>
       </c>
       <c r="D4" t="n">
-        <v>6.234034896151193</v>
+        <v>6.379105845414954</v>
       </c>
       <c r="E4" t="n">
-        <v>12.8178780117</v>
+        <v>12.98618392727585</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.698986252012792</v>
+        <v>1.569040635296623</v>
       </c>
       <c r="C5" t="n">
-        <v>5.744795262778156</v>
+        <v>5.941805109606173</v>
       </c>
       <c r="D5" t="n">
-        <v>6.60092240956291</v>
+        <v>6.752886306187208</v>
       </c>
       <c r="E5" t="n">
-        <v>14.04470392435386</v>
+        <v>14.26373205109</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.962483479687188</v>
+        <v>1.775304257566703</v>
       </c>
       <c r="C6" t="n">
-        <v>6.482275369716566</v>
+        <v>6.847019127342732</v>
       </c>
       <c r="D6" t="n">
-        <v>6.925432655724081</v>
+        <v>7.241302360810215</v>
       </c>
       <c r="E6" t="n">
-        <v>15.37019150512783</v>
+        <v>15.86362574571965</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.265463772053829</v>
+        <v>2.001936101624603</v>
       </c>
       <c r="C7" t="n">
-        <v>7.320333762138337</v>
+        <v>7.890708604472761</v>
       </c>
       <c r="D7" t="n">
-        <v>7.276907509498563</v>
+        <v>7.650964510557511</v>
       </c>
       <c r="E7" t="n">
-        <v>16.86270504369073</v>
+        <v>17.54360921665488</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.472222246374296</v>
+        <v>1.219577399060648</v>
       </c>
       <c r="C8" t="n">
-        <v>4.932270395615543</v>
+        <v>5.532788945649439</v>
       </c>
       <c r="D8" t="n">
-        <v>5.490423986553143</v>
+        <v>5.956283777532014</v>
       </c>
       <c r="E8" t="n">
-        <v>11.89491662854298</v>
+        <v>12.7086501222421</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.895869566494158</v>
+        <v>1.524405980129002</v>
       </c>
       <c r="C9" t="n">
-        <v>6.006932705808063</v>
+        <v>6.822435515593461</v>
       </c>
       <c r="D9" t="n">
-        <v>6.020465716723935</v>
+        <v>6.494965846209533</v>
       </c>
       <c r="E9" t="n">
-        <v>13.92326798902615</v>
+        <v>14.84180734193199</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.339255975889571</v>
+        <v>1.850518626865017</v>
       </c>
       <c r="C10" t="n">
-        <v>7.249310700954738</v>
+        <v>8.245064705880678</v>
       </c>
       <c r="D10" t="n">
-        <v>6.479835823412749</v>
+        <v>7.078726098331378</v>
       </c>
       <c r="E10" t="n">
-        <v>16.06840250025706</v>
+        <v>17.17430943107707</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.779684372929526</v>
+        <v>2.171884159949943</v>
       </c>
       <c r="C11" t="n">
-        <v>8.652235628308521</v>
+        <v>9.826239730378074</v>
       </c>
       <c r="D11" t="n">
-        <v>6.953072173488532</v>
+        <v>7.664458223422531</v>
       </c>
       <c r="E11" t="n">
-        <v>18.38499217472658</v>
+        <v>19.66258211375055</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.232909151886406</v>
+        <v>2.477506826671186</v>
       </c>
       <c r="C12" t="n">
-        <v>10.15519322408677</v>
+        <v>11.54363940050775</v>
       </c>
       <c r="D12" t="n">
-        <v>7.494681880841486</v>
+        <v>8.191372680187287</v>
       </c>
       <c r="E12" t="n">
-        <v>20.88278425681467</v>
+        <v>22.21251890736623</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.657419937800135</v>
+        <v>2.770339581019797</v>
       </c>
       <c r="C13" t="n">
-        <v>11.75223538169658</v>
+        <v>13.32488734213127</v>
       </c>
       <c r="D13" t="n">
-        <v>7.94807122080561</v>
+        <v>8.713343105387077</v>
       </c>
       <c r="E13" t="n">
-        <v>23.35772654030233</v>
+        <v>24.80857002853814</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.097798494434584</v>
+        <v>1.583961563508846</v>
       </c>
       <c r="C14" t="n">
-        <v>8.31944785551198</v>
+        <v>9.40218794609466</v>
       </c>
       <c r="D14" t="n">
-        <v>6.052072080122844</v>
+        <v>6.601340285694851</v>
       </c>
       <c r="E14" t="n">
-        <v>16.46931843006941</v>
+        <v>17.58748979529836</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.160384910580319</v>
+        <v>1.612383159546792</v>
       </c>
       <c r="C15" t="n">
-        <v>9.071142620222636</v>
+        <v>10.3081643625277</v>
       </c>
       <c r="D15" t="n">
-        <v>6.069606094120693</v>
+        <v>6.630606184758448</v>
       </c>
       <c r="E15" t="n">
-        <v>17.30113362492365</v>
+        <v>18.55115370683294</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.525496881789707</v>
+        <v>1.859410516889374</v>
       </c>
       <c r="C16" t="n">
-        <v>10.80671548169832</v>
+        <v>12.27503698312393</v>
       </c>
       <c r="D16" t="n">
-        <v>6.510027931722854</v>
+        <v>7.149842728057543</v>
       </c>
       <c r="E16" t="n">
-        <v>19.84224029521088</v>
+        <v>21.28429022807085</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.036576707597753</v>
+        <v>1.485197744461617</v>
       </c>
       <c r="C17" t="n">
-        <v>10.07045379089842</v>
+        <v>11.37144621361221</v>
       </c>
       <c r="D17" t="n">
-        <v>6.02857885756022</v>
+        <v>6.630890891592679</v>
       </c>
       <c r="E17" t="n">
-        <v>18.1356093560564</v>
+        <v>19.48753484966651</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.338041975140822</v>
+        <v>1.676972341009189</v>
       </c>
       <c r="C18" t="n">
-        <v>11.80691022530793</v>
+        <v>13.30480196758545</v>
       </c>
       <c r="D18" t="n">
-        <v>6.467901137733625</v>
+        <v>7.095228103270293</v>
       </c>
       <c r="E18" t="n">
-        <v>20.61285333818238</v>
+        <v>22.07700241186494</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.357814373904352</v>
+        <v>1.664867391815826</v>
       </c>
       <c r="C19" t="n">
-        <v>12.66786369202421</v>
+        <v>14.24187033381199</v>
       </c>
       <c r="D19" t="n">
-        <v>6.552557242270826</v>
+        <v>7.202405500142918</v>
       </c>
       <c r="E19" t="n">
-        <v>21.57823530819939</v>
+        <v>23.10914322577074</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.630622425960456</v>
+        <v>1.828082947646858</v>
       </c>
       <c r="C20" t="n">
-        <v>14.57032384574481</v>
+        <v>16.29187735000384</v>
       </c>
       <c r="D20" t="n">
-        <v>6.944755632640385</v>
+        <v>7.600945980681911</v>
       </c>
       <c r="E20" t="n">
-        <v>24.14570190434565</v>
+        <v>25.72090627833261</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.569588777118673</v>
+        <v>1.074591584637431</v>
       </c>
       <c r="C21" t="n">
-        <v>10.70316073385436</v>
+        <v>11.90892362925621</v>
       </c>
       <c r="D21" t="n">
-        <v>5.79330302023747</v>
+        <v>6.349620174325969</v>
       </c>
       <c r="E21" t="n">
-        <v>18.06605253121051</v>
+        <v>19.33313538821961</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_39_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.259834059232843</v>
+        <v>1.249378446182615</v>
       </c>
       <c r="C3" t="n">
-        <v>4.665104956765211</v>
+        <v>4.650791075237294</v>
       </c>
       <c r="D3" t="n">
-        <v>6.131471019638446</v>
+        <v>6.064064222264859</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0564100356365</v>
+        <v>11.96423374368477</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.394275922410535</v>
+        <v>1.369964017409719</v>
       </c>
       <c r="C4" t="n">
-        <v>5.21280215945036</v>
+        <v>5.210243992056958</v>
       </c>
       <c r="D4" t="n">
-        <v>6.379105845414954</v>
+        <v>6.333014649890027</v>
       </c>
       <c r="E4" t="n">
-        <v>12.98618392727585</v>
+        <v>12.91322265935671</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.569040635296623</v>
+        <v>1.540464454340036</v>
       </c>
       <c r="C5" t="n">
-        <v>5.941805109606173</v>
+        <v>5.993701810107341</v>
       </c>
       <c r="D5" t="n">
-        <v>6.752886306187208</v>
+        <v>6.615045836748683</v>
       </c>
       <c r="E5" t="n">
-        <v>14.26373205109</v>
+        <v>14.14921210119606</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.775304257566703</v>
+        <v>1.741480940125683</v>
       </c>
       <c r="C6" t="n">
-        <v>6.847019127342732</v>
+        <v>6.987264629776383</v>
       </c>
       <c r="D6" t="n">
-        <v>7.241302360810215</v>
+        <v>6.910830830087744</v>
       </c>
       <c r="E6" t="n">
-        <v>15.86362574571965</v>
+        <v>15.63957639998981</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.001936101624603</v>
+        <v>1.979520395145359</v>
       </c>
       <c r="C7" t="n">
-        <v>7.890708604472761</v>
+        <v>8.178215018282575</v>
       </c>
       <c r="D7" t="n">
-        <v>7.650964510557511</v>
+        <v>7.261923273172849</v>
       </c>
       <c r="E7" t="n">
-        <v>17.54360921665488</v>
+        <v>17.41965868660078</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.219577399060648</v>
+        <v>1.232851650010967</v>
       </c>
       <c r="C8" t="n">
-        <v>5.532788945649439</v>
+        <v>5.918290353160323</v>
       </c>
       <c r="D8" t="n">
-        <v>5.956283777532014</v>
+        <v>5.47367810700606</v>
       </c>
       <c r="E8" t="n">
-        <v>12.7086501222421</v>
+        <v>12.62482011017735</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.524405980129002</v>
+        <v>1.564451254470017</v>
       </c>
       <c r="C9" t="n">
-        <v>6.822435515593461</v>
+        <v>7.381433069688487</v>
       </c>
       <c r="D9" t="n">
-        <v>6.494965846209533</v>
+        <v>5.886424462107218</v>
       </c>
       <c r="E9" t="n">
-        <v>14.84180734193199</v>
+        <v>14.83230878626572</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.850518626865017</v>
+        <v>1.905606245813781</v>
       </c>
       <c r="C10" t="n">
-        <v>8.245064705880678</v>
+        <v>9.015132990636321</v>
       </c>
       <c r="D10" t="n">
-        <v>7.078726098331378</v>
+        <v>6.288285741958902</v>
       </c>
       <c r="E10" t="n">
-        <v>17.17430943107707</v>
+        <v>17.209024978409</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.171884159949943</v>
+        <v>2.244788796307586</v>
       </c>
       <c r="C11" t="n">
-        <v>9.826239730378074</v>
+        <v>10.74790264931905</v>
       </c>
       <c r="D11" t="n">
-        <v>7.664458223422531</v>
+        <v>6.663949372387839</v>
       </c>
       <c r="E11" t="n">
-        <v>19.66258211375055</v>
+        <v>19.65664081801448</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.477506826671186</v>
+        <v>2.566582180759873</v>
       </c>
       <c r="C12" t="n">
-        <v>11.54363940050775</v>
+        <v>12.55839411234709</v>
       </c>
       <c r="D12" t="n">
-        <v>8.191372680187287</v>
+        <v>7.055322792887417</v>
       </c>
       <c r="E12" t="n">
-        <v>22.21251890736623</v>
+        <v>22.18029908599438</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.770339581019797</v>
+        <v>2.863040682765867</v>
       </c>
       <c r="C13" t="n">
-        <v>13.32488734213127</v>
+        <v>14.45944569908149</v>
       </c>
       <c r="D13" t="n">
-        <v>8.713343105387077</v>
+        <v>7.394621014784927</v>
       </c>
       <c r="E13" t="n">
-        <v>24.80857002853814</v>
+        <v>24.71710739663229</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.583961563508846</v>
+        <v>1.628552544235737</v>
       </c>
       <c r="C14" t="n">
-        <v>9.40218794609466</v>
+        <v>10.09604795354814</v>
       </c>
       <c r="D14" t="n">
-        <v>6.601340285694851</v>
+        <v>5.610472145275587</v>
       </c>
       <c r="E14" t="n">
-        <v>17.58748979529836</v>
+        <v>17.33507264305946</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.612383159546792</v>
+        <v>1.650308073361846</v>
       </c>
       <c r="C15" t="n">
-        <v>10.3081643625277</v>
+        <v>11.02719638111806</v>
       </c>
       <c r="D15" t="n">
-        <v>6.630606184758448</v>
+        <v>5.530224087930454</v>
       </c>
       <c r="E15" t="n">
-        <v>18.55115370683294</v>
+        <v>18.20772854241036</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.859410516889374</v>
+        <v>1.895892261579185</v>
       </c>
       <c r="C16" t="n">
-        <v>12.27503698312393</v>
+        <v>13.08278954174708</v>
       </c>
       <c r="D16" t="n">
-        <v>7.149842728057543</v>
+        <v>5.867631138925996</v>
       </c>
       <c r="E16" t="n">
-        <v>21.28429022807085</v>
+        <v>20.84631294225226</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.485197744461617</v>
+        <v>1.511066796468521</v>
       </c>
       <c r="C17" t="n">
-        <v>11.37144621361221</v>
+        <v>12.04874413729504</v>
       </c>
       <c r="D17" t="n">
-        <v>6.630890891592679</v>
+        <v>5.365172663892479</v>
       </c>
       <c r="E17" t="n">
-        <v>19.48753484966651</v>
+        <v>18.92498359765604</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.676972341009189</v>
+        <v>1.717194544452181</v>
       </c>
       <c r="C18" t="n">
-        <v>13.30480196758545</v>
+        <v>14.05301152794603</v>
       </c>
       <c r="D18" t="n">
-        <v>7.095228103270293</v>
+        <v>5.724070172133986</v>
       </c>
       <c r="E18" t="n">
-        <v>22.07700241186494</v>
+        <v>21.4942762445322</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.664867391815826</v>
+        <v>1.712835584645325</v>
       </c>
       <c r="C19" t="n">
-        <v>14.24187033381199</v>
+        <v>14.99569549104086</v>
       </c>
       <c r="D19" t="n">
-        <v>7.202405500142918</v>
+        <v>5.751048599046689</v>
       </c>
       <c r="E19" t="n">
-        <v>23.10914322577074</v>
+        <v>22.45957967473288</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.828082947646858</v>
+        <v>1.894409822545773</v>
       </c>
       <c r="C20" t="n">
-        <v>16.29187735000384</v>
+        <v>17.096625760652</v>
       </c>
       <c r="D20" t="n">
-        <v>7.600945980681911</v>
+        <v>6.067780043390794</v>
       </c>
       <c r="E20" t="n">
-        <v>25.72090627833261</v>
+        <v>25.05881562658856</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.074591584637431</v>
+        <v>1.120311575224205</v>
       </c>
       <c r="C21" t="n">
-        <v>11.90892362925621</v>
+        <v>12.41599631849969</v>
       </c>
       <c r="D21" t="n">
-        <v>6.349620174325969</v>
+        <v>5.017221642553324</v>
       </c>
       <c r="E21" t="n">
-        <v>19.33313538821961</v>
+        <v>18.55352953627722</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_39_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249378446182615</v>
+        <v>2.605793548403584</v>
       </c>
       <c r="C3" t="n">
-        <v>4.650791075237294</v>
+        <v>7.690714160114744</v>
       </c>
       <c r="D3" t="n">
-        <v>6.064064222264859</v>
+        <v>8.244440135964947</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96423374368477</v>
+        <v>18.54094784448327</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.369964017409719</v>
+        <v>1.092553007399761</v>
       </c>
       <c r="C4" t="n">
-        <v>5.210243992056958</v>
+        <v>4.424792033699728</v>
       </c>
       <c r="D4" t="n">
-        <v>6.333014649890027</v>
+        <v>5.878243527593879</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91322265935671</v>
+        <v>11.39558856869337</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.540464454340036</v>
+        <v>1.201375402185256</v>
       </c>
       <c r="C5" t="n">
-        <v>5.993701810107341</v>
+        <v>4.960174369493825</v>
       </c>
       <c r="D5" t="n">
-        <v>6.615045836748683</v>
+        <v>6.222985223573985</v>
       </c>
       <c r="E5" t="n">
-        <v>14.14921210119606</v>
+        <v>12.38453499525307</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.741480940125683</v>
+        <v>1.318100812241738</v>
       </c>
       <c r="C6" t="n">
-        <v>6.987264629776383</v>
+        <v>5.605872385792354</v>
       </c>
       <c r="D6" t="n">
-        <v>6.910830830087744</v>
+        <v>6.662268605640403</v>
       </c>
       <c r="E6" t="n">
-        <v>15.63957639998981</v>
+        <v>13.5862418036745</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.979520395145359</v>
+        <v>1.439433979864113</v>
       </c>
       <c r="C7" t="n">
-        <v>8.178215018282575</v>
+        <v>6.422227106325106</v>
       </c>
       <c r="D7" t="n">
-        <v>7.261923273172849</v>
+        <v>7.071135583085277</v>
       </c>
       <c r="E7" t="n">
-        <v>17.41965868660078</v>
+        <v>14.9327966692745</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.232851650010967</v>
+        <v>1.564038765708762</v>
       </c>
       <c r="C8" t="n">
-        <v>5.918290353160323</v>
+        <v>7.408070601401572</v>
       </c>
       <c r="D8" t="n">
-        <v>5.47367810700606</v>
+        <v>7.540067021321335</v>
       </c>
       <c r="E8" t="n">
-        <v>12.62482011017735</v>
+        <v>16.51217638843167</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.564451254470017</v>
+        <v>1.691196806010623</v>
       </c>
       <c r="C9" t="n">
-        <v>7.381433069688487</v>
+        <v>8.544030756569986</v>
       </c>
       <c r="D9" t="n">
-        <v>5.886424462107218</v>
+        <v>8.133016468830924</v>
       </c>
       <c r="E9" t="n">
-        <v>14.83230878626572</v>
+        <v>18.36824403141153</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.905606245813781</v>
+        <v>1.05943340008386</v>
       </c>
       <c r="C10" t="n">
-        <v>9.015132990636321</v>
+        <v>6.466261619067532</v>
       </c>
       <c r="D10" t="n">
-        <v>6.288285741958902</v>
+        <v>6.421395748983453</v>
       </c>
       <c r="E10" t="n">
-        <v>17.209024978409</v>
+        <v>13.94709076813484</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.244788796307586</v>
+        <v>0.9861066640536663</v>
       </c>
       <c r="C11" t="n">
-        <v>10.74790264931905</v>
+        <v>6.853266564081624</v>
       </c>
       <c r="D11" t="n">
-        <v>6.663949372387839</v>
+        <v>6.368057396211722</v>
       </c>
       <c r="E11" t="n">
-        <v>19.65664081801448</v>
+        <v>14.20743062434701</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.566582180759873</v>
+        <v>1.056586331741545</v>
       </c>
       <c r="C12" t="n">
-        <v>12.55839411234709</v>
+        <v>8.137853982657449</v>
       </c>
       <c r="D12" t="n">
-        <v>7.055322792887417</v>
+        <v>6.852117919267655</v>
       </c>
       <c r="E12" t="n">
-        <v>22.18029908599438</v>
+        <v>16.04655823366665</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.863040682765867</v>
+        <v>0.8265333922053897</v>
       </c>
       <c r="C13" t="n">
-        <v>14.45944569908149</v>
+        <v>7.811638855490318</v>
       </c>
       <c r="D13" t="n">
-        <v>7.394621014784927</v>
+        <v>6.344907785345583</v>
       </c>
       <c r="E13" t="n">
-        <v>24.71710739663229</v>
+        <v>14.98308003304129</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.628552544235737</v>
+        <v>0.8900131987619885</v>
       </c>
       <c r="C14" t="n">
-        <v>10.09604795354814</v>
+        <v>9.186949579415591</v>
       </c>
       <c r="D14" t="n">
-        <v>5.610472145275587</v>
+        <v>6.830274032848163</v>
       </c>
       <c r="E14" t="n">
-        <v>17.33507264305946</v>
+        <v>16.90723681102574</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.650308073361846</v>
+        <v>0.8585089149327083</v>
       </c>
       <c r="C15" t="n">
-        <v>11.02719638111806</v>
+        <v>9.955294785190272</v>
       </c>
       <c r="D15" t="n">
-        <v>5.530224087930454</v>
+        <v>6.971871504231682</v>
       </c>
       <c r="E15" t="n">
-        <v>18.20772854241036</v>
+        <v>17.78567520435466</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.895892261579185</v>
+        <v>0.935664467009465</v>
       </c>
       <c r="C16" t="n">
-        <v>13.08278954174708</v>
+        <v>11.65199043757778</v>
       </c>
       <c r="D16" t="n">
-        <v>5.867631138925996</v>
+        <v>7.448883078771122</v>
       </c>
       <c r="E16" t="n">
-        <v>20.84631294225226</v>
+        <v>20.03653798335836</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.511066796468521</v>
+        <v>0.5644067551714913</v>
       </c>
       <c r="C17" t="n">
-        <v>12.04874413729504</v>
+        <v>8.783186201090004</v>
       </c>
       <c r="D17" t="n">
-        <v>5.365172663892479</v>
+        <v>6.243679779560694</v>
       </c>
       <c r="E17" t="n">
-        <v>18.92498359765604</v>
+        <v>15.59127273582219</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.717194544452181</v>
+        <v>0.4390572082932586</v>
       </c>
       <c r="C18" t="n">
-        <v>14.05301152794603</v>
+        <v>7.844291784133567</v>
       </c>
       <c r="D18" t="n">
-        <v>5.724070172133986</v>
+        <v>5.766501307911533</v>
       </c>
       <c r="E18" t="n">
-        <v>21.4942762445322</v>
+        <v>14.04985030033836</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.712835584645325</v>
+        <v>0.5120796025351363</v>
       </c>
       <c r="C19" t="n">
-        <v>14.99569549104086</v>
+        <v>9.676233000258115</v>
       </c>
       <c r="D19" t="n">
-        <v>5.751048599046689</v>
+        <v>6.361469869116228</v>
       </c>
       <c r="E19" t="n">
-        <v>22.45957967473288</v>
+        <v>16.54978247190948</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.894409822545773</v>
+        <v>0.5804779650900116</v>
       </c>
       <c r="C20" t="n">
-        <v>17.096625760652</v>
+        <v>11.58153040484399</v>
       </c>
       <c r="D20" t="n">
-        <v>6.067780043390794</v>
+        <v>6.950223967353039</v>
       </c>
       <c r="E20" t="n">
-        <v>25.05881562658856</v>
+        <v>19.11223233728704</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.120311575224205</v>
+        <v>0.640992893579785</v>
       </c>
       <c r="C21" t="n">
-        <v>12.41599631849969</v>
+        <v>13.50674747034902</v>
       </c>
       <c r="D21" t="n">
-        <v>5.017221642553324</v>
+        <v>7.457090489578626</v>
       </c>
       <c r="E21" t="n">
-        <v>18.55352953627722</v>
+        <v>21.60483085350743</v>
       </c>
     </row>
   </sheetData>
